--- a/artfynd/A 55743-2023 artfynd.xlsx
+++ b/artfynd/A 55743-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 55743-2023 artfynd.xlsx
+++ b/artfynd/A 55743-2023 artfynd.xlsx
@@ -2557,7 +2557,7 @@
         <v>121377182</v>
       </c>
       <c r="B17" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>

--- a/artfynd/A 55743-2023 artfynd.xlsx
+++ b/artfynd/A 55743-2023 artfynd.xlsx
@@ -2557,7 +2557,7 @@
         <v>121377182</v>
       </c>
       <c r="B17" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>

--- a/artfynd/A 55743-2023 artfynd.xlsx
+++ b/artfynd/A 55743-2023 artfynd.xlsx
@@ -2557,7 +2557,7 @@
         <v>121377182</v>
       </c>
       <c r="B17" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>

--- a/artfynd/A 55743-2023 artfynd.xlsx
+++ b/artfynd/A 55743-2023 artfynd.xlsx
@@ -2557,7 +2557,7 @@
         <v>121377182</v>
       </c>
       <c r="B17" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>

--- a/artfynd/A 55743-2023 artfynd.xlsx
+++ b/artfynd/A 55743-2023 artfynd.xlsx
@@ -2557,7 +2557,7 @@
         <v>121377182</v>
       </c>
       <c r="B17" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>

--- a/artfynd/A 55743-2023 artfynd.xlsx
+++ b/artfynd/A 55743-2023 artfynd.xlsx
@@ -2557,7 +2557,7 @@
         <v>121377182</v>
       </c>
       <c r="B17" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>

--- a/artfynd/A 55743-2023 artfynd.xlsx
+++ b/artfynd/A 55743-2023 artfynd.xlsx
@@ -2557,7 +2557,7 @@
         <v>121377182</v>
       </c>
       <c r="B17" t="n">
-        <v>98105</v>
+        <v>98113</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>

--- a/artfynd/A 55743-2023 artfynd.xlsx
+++ b/artfynd/A 55743-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2685,6 +2685,566 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>123336769</v>
+      </c>
+      <c r="B18" t="n">
+        <v>98365</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Knärotkulle, Speleboda, Sm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>463056</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6295451</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Alvesta</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Vislanda</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Dellokal</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Caroline Mortlock</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Caroline Mortlock, Per Darell</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>123334925</v>
+      </c>
+      <c r="B19" t="n">
+        <v>98365</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Knärotkulle, Speleboda, Sm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>463069</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6295438</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Alvesta</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Vislanda</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Dellokal</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Caroline Mortlock</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Caroline Mortlock, Per Darell</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>123336849</v>
+      </c>
+      <c r="B20" t="n">
+        <v>98365</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Knärotkulle, Speleboda, Sm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>463066</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6295448</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Alvesta</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Vislanda</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Dellokal</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Caroline Mortlock</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Caroline Mortlock, Per Darell</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>123334183</v>
+      </c>
+      <c r="B21" t="n">
+        <v>98365</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Knärotkulle, Speleboda, Sm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>463078</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6295459</v>
+      </c>
+      <c r="S21" t="n">
+        <v>75</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Alvesta</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Vislanda</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Riklig med bladrosetter påträffade på 4 olika dellokaler. Totalt 50 vinterståndare.</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Caroline Mortlock</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Caroline Mortlock, Per Darell</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>123334834</v>
+      </c>
+      <c r="B22" t="n">
+        <v>98365</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Knärotkulle, Speleboda, Sm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>463076</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6295442</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Alvesta</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Vislanda</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Dellokal</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Caroline Mortlock</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Caroline Mortlock, Per Darell</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 55743-2023 artfynd.xlsx
+++ b/artfynd/A 55743-2023 artfynd.xlsx
@@ -2687,10 +2687,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123336769</v>
+        <v>123334834</v>
       </c>
       <c r="B18" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2731,10 +2731,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>463056</v>
+        <v>463076</v>
       </c>
       <c r="R18" t="n">
-        <v>6295451</v>
+        <v>6295442</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2799,10 +2799,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123334925</v>
+        <v>123336849</v>
       </c>
       <c r="B19" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2843,10 +2843,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>463069</v>
+        <v>463066</v>
       </c>
       <c r="R19" t="n">
-        <v>6295438</v>
+        <v>6295448</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2911,10 +2911,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123336849</v>
+        <v>123336769</v>
       </c>
       <c r="B20" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2955,10 +2955,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>463066</v>
+        <v>463056</v>
       </c>
       <c r="R20" t="n">
-        <v>6295448</v>
+        <v>6295451</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -3026,7 +3026,7 @@
         <v>123334183</v>
       </c>
       <c r="B21" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3135,10 +3135,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123334834</v>
+        <v>123334925</v>
       </c>
       <c r="B22" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3179,10 +3179,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>463076</v>
+        <v>463069</v>
       </c>
       <c r="R22" t="n">
-        <v>6295442</v>
+        <v>6295438</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Caroline Mortlock, Per Darell</t>
+          <t>Per Darell, Caroline Mortlock</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>

--- a/artfynd/A 55743-2023 artfynd.xlsx
+++ b/artfynd/A 55743-2023 artfynd.xlsx
@@ -2690,7 +2690,7 @@
         <v>123334834</v>
       </c>
       <c r="B18" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2799,10 +2799,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123336849</v>
+        <v>123336769</v>
       </c>
       <c r="B19" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2843,10 +2843,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>463066</v>
+        <v>463056</v>
       </c>
       <c r="R19" t="n">
-        <v>6295448</v>
+        <v>6295451</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2911,10 +2911,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123336769</v>
+        <v>123334925</v>
       </c>
       <c r="B20" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2955,10 +2955,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>463056</v>
+        <v>463069</v>
       </c>
       <c r="R20" t="n">
-        <v>6295451</v>
+        <v>6295438</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -3023,10 +3023,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123334183</v>
+        <v>123336849</v>
       </c>
       <c r="B21" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3067,13 +3067,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>463078</v>
+        <v>463066</v>
       </c>
       <c r="R21" t="n">
-        <v>6295459</v>
+        <v>6295448</v>
       </c>
       <c r="S21" t="n">
-        <v>75</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3107,7 +3107,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Riklig med bladrosetter påträffade på 4 olika dellokaler. Totalt 50 vinterståndare.</t>
+          <t>Dellokal</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3135,10 +3135,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123334925</v>
+        <v>123334183</v>
       </c>
       <c r="B22" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3179,13 +3179,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>463069</v>
+        <v>463078</v>
       </c>
       <c r="R22" t="n">
-        <v>6295438</v>
+        <v>6295459</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>75</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3219,7 +3219,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Dellokal</t>
+          <t>Riklig med bladrosetter påträffade på 4 olika dellokaler. Totalt 50 vinterståndare.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Per Darell, Caroline Mortlock</t>
+          <t>Caroline Mortlock, Per Darell</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>

--- a/artfynd/A 55743-2023 artfynd.xlsx
+++ b/artfynd/A 55743-2023 artfynd.xlsx
@@ -2687,10 +2687,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123334834</v>
+        <v>123334183</v>
       </c>
       <c r="B18" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2731,13 +2731,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>463076</v>
+        <v>463078</v>
       </c>
       <c r="R18" t="n">
-        <v>6295442</v>
+        <v>6295459</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>75</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2771,7 +2771,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Dellokal</t>
+          <t>Riklig med bladrosetter påträffade på 4 olika dellokaler. Totalt 50 vinterståndare.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2799,10 +2799,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123336769</v>
+        <v>123336849</v>
       </c>
       <c r="B19" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2843,10 +2843,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>463056</v>
+        <v>463066</v>
       </c>
       <c r="R19" t="n">
-        <v>6295451</v>
+        <v>6295448</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2911,10 +2911,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123334925</v>
+        <v>123334834</v>
       </c>
       <c r="B20" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2955,10 +2955,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>463069</v>
+        <v>463076</v>
       </c>
       <c r="R20" t="n">
-        <v>6295438</v>
+        <v>6295442</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -3023,10 +3023,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123336849</v>
+        <v>123336769</v>
       </c>
       <c r="B21" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3067,10 +3067,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>463066</v>
+        <v>463056</v>
       </c>
       <c r="R21" t="n">
-        <v>6295448</v>
+        <v>6295451</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3135,10 +3135,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123334183</v>
+        <v>123334925</v>
       </c>
       <c r="B22" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3179,13 +3179,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>463078</v>
+        <v>463069</v>
       </c>
       <c r="R22" t="n">
-        <v>6295459</v>
+        <v>6295438</v>
       </c>
       <c r="S22" t="n">
-        <v>75</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3219,7 +3219,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Riklig med bladrosetter påträffade på 4 olika dellokaler. Totalt 50 vinterståndare.</t>
+          <t>Dellokal</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 55743-2023 artfynd.xlsx
+++ b/artfynd/A 55743-2023 artfynd.xlsx
@@ -2687,10 +2687,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123334183</v>
+        <v>123336849</v>
       </c>
       <c r="B18" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2731,13 +2731,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>463078</v>
+        <v>463066</v>
       </c>
       <c r="R18" t="n">
-        <v>6295459</v>
+        <v>6295448</v>
       </c>
       <c r="S18" t="n">
-        <v>75</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2771,7 +2771,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Riklig med bladrosetter påträffade på 4 olika dellokaler. Totalt 50 vinterståndare.</t>
+          <t>Dellokal</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2799,10 +2799,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123336849</v>
+        <v>123334925</v>
       </c>
       <c r="B19" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2843,10 +2843,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>463066</v>
+        <v>463069</v>
       </c>
       <c r="R19" t="n">
-        <v>6295448</v>
+        <v>6295438</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2914,7 +2914,7 @@
         <v>123334834</v>
       </c>
       <c r="B20" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3026,7 +3026,7 @@
         <v>123336769</v>
       </c>
       <c r="B21" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3135,10 +3135,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123334925</v>
+        <v>123334183</v>
       </c>
       <c r="B22" t="n">
-        <v>98376</v>
+        <v>98379</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3179,13 +3179,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>463069</v>
+        <v>463078</v>
       </c>
       <c r="R22" t="n">
-        <v>6295438</v>
+        <v>6295459</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>75</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3219,7 +3219,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Dellokal</t>
+          <t>Riklig med bladrosetter påträffade på 4 olika dellokaler. Totalt 50 vinterståndare.</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 55743-2023 artfynd.xlsx
+++ b/artfynd/A 55743-2023 artfynd.xlsx
@@ -2687,10 +2687,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123336849</v>
+        <v>123336769</v>
       </c>
       <c r="B18" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2731,10 +2731,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>463066</v>
+        <v>463056</v>
       </c>
       <c r="R18" t="n">
-        <v>6295448</v>
+        <v>6295451</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2799,10 +2799,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123334925</v>
+        <v>123334183</v>
       </c>
       <c r="B19" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2843,13 +2843,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>463069</v>
+        <v>463078</v>
       </c>
       <c r="R19" t="n">
-        <v>6295438</v>
+        <v>6295459</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>75</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2883,7 +2883,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Dellokal</t>
+          <t>Riklig med bladrosetter påträffade på 4 olika dellokaler. Totalt 50 vinterståndare.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2911,10 +2911,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123334834</v>
+        <v>123336849</v>
       </c>
       <c r="B20" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2955,10 +2955,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>463076</v>
+        <v>463066</v>
       </c>
       <c r="R20" t="n">
-        <v>6295442</v>
+        <v>6295448</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -3023,10 +3023,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123336769</v>
+        <v>123334834</v>
       </c>
       <c r="B21" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3067,10 +3067,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>463056</v>
+        <v>463076</v>
       </c>
       <c r="R21" t="n">
-        <v>6295451</v>
+        <v>6295442</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3135,10 +3135,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123334183</v>
+        <v>123334925</v>
       </c>
       <c r="B22" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3179,13 +3179,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>463078</v>
+        <v>463069</v>
       </c>
       <c r="R22" t="n">
-        <v>6295459</v>
+        <v>6295438</v>
       </c>
       <c r="S22" t="n">
-        <v>75</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3219,7 +3219,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Riklig med bladrosetter påträffade på 4 olika dellokaler. Totalt 50 vinterståndare.</t>
+          <t>Dellokal</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 55743-2023 artfynd.xlsx
+++ b/artfynd/A 55743-2023 artfynd.xlsx
@@ -2911,7 +2911,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123336849</v>
+        <v>123334834</v>
       </c>
       <c r="B20" t="n">
         <v>98396</v>
@@ -2955,10 +2955,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>463066</v>
+        <v>463076</v>
       </c>
       <c r="R20" t="n">
-        <v>6295448</v>
+        <v>6295442</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -3023,7 +3023,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123334834</v>
+        <v>123336849</v>
       </c>
       <c r="B21" t="n">
         <v>98396</v>
@@ -3067,10 +3067,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>463076</v>
+        <v>463066</v>
       </c>
       <c r="R21" t="n">
-        <v>6295442</v>
+        <v>6295448</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>

--- a/artfynd/A 55743-2023 artfynd.xlsx
+++ b/artfynd/A 55743-2023 artfynd.xlsx
@@ -2911,7 +2911,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123334834</v>
+        <v>123336849</v>
       </c>
       <c r="B20" t="n">
         <v>98396</v>
@@ -2955,10 +2955,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>463076</v>
+        <v>463066</v>
       </c>
       <c r="R20" t="n">
-        <v>6295442</v>
+        <v>6295448</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -3023,7 +3023,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123336849</v>
+        <v>123334834</v>
       </c>
       <c r="B21" t="n">
         <v>98396</v>
@@ -3067,10 +3067,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>463066</v>
+        <v>463076</v>
       </c>
       <c r="R21" t="n">
-        <v>6295448</v>
+        <v>6295442</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>

--- a/artfynd/A 55743-2023 artfynd.xlsx
+++ b/artfynd/A 55743-2023 artfynd.xlsx
@@ -2690,7 +2690,7 @@
         <v>123336769</v>
       </c>
       <c r="B18" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2799,10 +2799,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123334183</v>
+        <v>123336849</v>
       </c>
       <c r="B19" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2843,13 +2843,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>463078</v>
+        <v>463066</v>
       </c>
       <c r="R19" t="n">
-        <v>6295459</v>
+        <v>6295448</v>
       </c>
       <c r="S19" t="n">
-        <v>75</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2883,7 +2883,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Riklig med bladrosetter påträffade på 4 olika dellokaler. Totalt 50 vinterståndare.</t>
+          <t>Dellokal</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2911,10 +2911,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123334834</v>
+        <v>123334925</v>
       </c>
       <c r="B20" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2955,10 +2955,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>463076</v>
+        <v>463069</v>
       </c>
       <c r="R20" t="n">
-        <v>6295442</v>
+        <v>6295438</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -3023,10 +3023,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123336849</v>
+        <v>123334183</v>
       </c>
       <c r="B21" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3067,13 +3067,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>463066</v>
+        <v>463078</v>
       </c>
       <c r="R21" t="n">
-        <v>6295448</v>
+        <v>6295459</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>75</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3107,7 +3107,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Dellokal</t>
+          <t>Riklig med bladrosetter påträffade på 4 olika dellokaler. Totalt 50 vinterståndare.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3135,10 +3135,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123334925</v>
+        <v>123334834</v>
       </c>
       <c r="B22" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3179,10 +3179,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>463069</v>
+        <v>463076</v>
       </c>
       <c r="R22" t="n">
-        <v>6295438</v>
+        <v>6295442</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>

--- a/artfynd/A 55743-2023 artfynd.xlsx
+++ b/artfynd/A 55743-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2554,10 +2554,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121377182</v>
+        <v>123336769</v>
       </c>
       <c r="B17" t="n">
-        <v>98113</v>
+        <v>98504</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2587,36 +2587,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Speleboda, 300 m S om, Sm</t>
+          <t>Knärotkulle, Speleboda, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>463069</v>
+        <v>463056</v>
       </c>
       <c r="R17" t="n">
-        <v>6295455</v>
+        <v>6295451</v>
       </c>
       <c r="S17" t="n">
-        <v>43</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2638,24 +2626,19 @@
           <t>Vislanda</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>G-Alv-0295</t>
-        </is>
-      </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-01-23</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-01-23</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Över 200 plantor varav drygt 80 blommade förra året. Utspritt inom ett område se foto, och koordinater 463069/6295439, 463065/6295444, 463069/6295439, 463068/6295440</t>
+          <t>Dellokal</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2671,26 +2654,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Uno Pettersson</t>
+          <t>Caroline Mortlock</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Per Darell</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Caroline Mortlock, Per Darell</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123336769</v>
+        <v>123334834</v>
       </c>
       <c r="B18" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2731,10 +2710,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>463056</v>
+        <v>463076</v>
       </c>
       <c r="R18" t="n">
-        <v>6295451</v>
+        <v>6295442</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2799,10 +2778,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123336849</v>
+        <v>123334925</v>
       </c>
       <c r="B19" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2843,10 +2822,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>463066</v>
+        <v>463069</v>
       </c>
       <c r="R19" t="n">
-        <v>6295448</v>
+        <v>6295438</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2911,10 +2890,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123334925</v>
+        <v>123336849</v>
       </c>
       <c r="B20" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2955,10 +2934,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>463069</v>
+        <v>463066</v>
       </c>
       <c r="R20" t="n">
-        <v>6295438</v>
+        <v>6295448</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -3026,7 +3005,7 @@
         <v>123334183</v>
       </c>
       <c r="B21" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3128,122 +3107,10 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Caroline Mortlock, Per Darell</t>
+          <t>Per Darell, Caroline Mortlock</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>123334834</v>
-      </c>
-      <c r="B22" t="n">
-        <v>98502</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>Knärotkulle, Speleboda, Sm</t>
-        </is>
-      </c>
-      <c r="Q22" t="n">
-        <v>463076</v>
-      </c>
-      <c r="R22" t="n">
-        <v>6295442</v>
-      </c>
-      <c r="S22" t="n">
-        <v>5</v>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>Kronoberg</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>Alvesta</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>Småland</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>Vislanda</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>2025-03-20</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Dellokal</t>
-        </is>
-      </c>
-      <c r="AD22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF22" t="inlineStr"/>
-      <c r="AG22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT22" t="inlineStr"/>
-      <c r="AW22" t="inlineStr">
-        <is>
-          <t>Caroline Mortlock</t>
-        </is>
-      </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>Caroline Mortlock, Per Darell</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 55743-2023 artfynd.xlsx
+++ b/artfynd/A 55743-2023 artfynd.xlsx
@@ -2554,10 +2554,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123336769</v>
+        <v>123336849</v>
       </c>
       <c r="B17" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2598,10 +2598,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>463056</v>
+        <v>463066</v>
       </c>
       <c r="R17" t="n">
-        <v>6295451</v>
+        <v>6295448</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2666,10 +2666,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123334834</v>
+        <v>123336769</v>
       </c>
       <c r="B18" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2710,10 +2710,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>463076</v>
+        <v>463056</v>
       </c>
       <c r="R18" t="n">
-        <v>6295442</v>
+        <v>6295451</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2778,10 +2778,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123334925</v>
+        <v>123334183</v>
       </c>
       <c r="B19" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2822,13 +2822,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>463069</v>
+        <v>463078</v>
       </c>
       <c r="R19" t="n">
-        <v>6295438</v>
+        <v>6295459</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>75</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2862,7 +2862,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Dellokal</t>
+          <t>Riklig med bladrosetter påträffade på 4 olika dellokaler. Totalt 50 vinterståndare.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2890,10 +2890,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123336849</v>
+        <v>123334925</v>
       </c>
       <c r="B20" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2934,10 +2934,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>463066</v>
+        <v>463069</v>
       </c>
       <c r="R20" t="n">
-        <v>6295448</v>
+        <v>6295438</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -3002,10 +3002,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123334183</v>
+        <v>123334834</v>
       </c>
       <c r="B21" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3046,13 +3046,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>463078</v>
+        <v>463076</v>
       </c>
       <c r="R21" t="n">
-        <v>6295459</v>
+        <v>6295442</v>
       </c>
       <c r="S21" t="n">
-        <v>75</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Riklig med bladrosetter påträffade på 4 olika dellokaler. Totalt 50 vinterståndare.</t>
+          <t>Dellokal</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3107,7 +3107,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Per Darell, Caroline Mortlock</t>
+          <t>Caroline Mortlock, Per Darell</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>

--- a/artfynd/A 55743-2023 artfynd.xlsx
+++ b/artfynd/A 55743-2023 artfynd.xlsx
@@ -2554,7 +2554,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123336849</v>
+        <v>123334834</v>
       </c>
       <c r="B17" t="n">
         <v>98079</v>
@@ -2598,10 +2598,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>463066</v>
+        <v>463076</v>
       </c>
       <c r="R17" t="n">
-        <v>6295448</v>
+        <v>6295442</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2890,7 +2890,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123334925</v>
+        <v>123336849</v>
       </c>
       <c r="B20" t="n">
         <v>98079</v>
@@ -2934,10 +2934,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>463069</v>
+        <v>463066</v>
       </c>
       <c r="R20" t="n">
-        <v>6295438</v>
+        <v>6295448</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -3002,7 +3002,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123334834</v>
+        <v>123334925</v>
       </c>
       <c r="B21" t="n">
         <v>98079</v>
@@ -3046,10 +3046,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>463076</v>
+        <v>463069</v>
       </c>
       <c r="R21" t="n">
-        <v>6295442</v>
+        <v>6295438</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>

--- a/artfynd/A 55743-2023 artfynd.xlsx
+++ b/artfynd/A 55743-2023 artfynd.xlsx
@@ -2554,7 +2554,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123334834</v>
+        <v>123334925</v>
       </c>
       <c r="B17" t="n">
         <v>98079</v>
@@ -2598,10 +2598,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>463076</v>
+        <v>463069</v>
       </c>
       <c r="R17" t="n">
-        <v>6295442</v>
+        <v>6295438</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2666,7 +2666,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123336769</v>
+        <v>123336849</v>
       </c>
       <c r="B18" t="n">
         <v>98079</v>
@@ -2710,10 +2710,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>463056</v>
+        <v>463066</v>
       </c>
       <c r="R18" t="n">
-        <v>6295451</v>
+        <v>6295448</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2890,7 +2890,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123336849</v>
+        <v>123336769</v>
       </c>
       <c r="B20" t="n">
         <v>98079</v>
@@ -2934,10 +2934,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>463066</v>
+        <v>463056</v>
       </c>
       <c r="R20" t="n">
-        <v>6295448</v>
+        <v>6295451</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -3002,7 +3002,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123334925</v>
+        <v>123334834</v>
       </c>
       <c r="B21" t="n">
         <v>98079</v>
@@ -3046,10 +3046,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>463069</v>
+        <v>463076</v>
       </c>
       <c r="R21" t="n">
-        <v>6295438</v>
+        <v>6295442</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>

--- a/artfynd/A 55743-2023 artfynd.xlsx
+++ b/artfynd/A 55743-2023 artfynd.xlsx
@@ -2554,7 +2554,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123334925</v>
+        <v>123336849</v>
       </c>
       <c r="B17" t="n">
         <v>98079</v>
@@ -2598,10 +2598,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>463069</v>
+        <v>463066</v>
       </c>
       <c r="R17" t="n">
-        <v>6295438</v>
+        <v>6295448</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2666,7 +2666,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123336849</v>
+        <v>123336769</v>
       </c>
       <c r="B18" t="n">
         <v>98079</v>
@@ -2710,10 +2710,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>463066</v>
+        <v>463056</v>
       </c>
       <c r="R18" t="n">
-        <v>6295448</v>
+        <v>6295451</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2890,7 +2890,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123336769</v>
+        <v>123334834</v>
       </c>
       <c r="B20" t="n">
         <v>98079</v>
@@ -2934,10 +2934,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>463056</v>
+        <v>463076</v>
       </c>
       <c r="R20" t="n">
-        <v>6295451</v>
+        <v>6295442</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -3002,7 +3002,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123334834</v>
+        <v>123334925</v>
       </c>
       <c r="B21" t="n">
         <v>98079</v>
@@ -3046,10 +3046,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>463076</v>
+        <v>463069</v>
       </c>
       <c r="R21" t="n">
-        <v>6295442</v>
+        <v>6295438</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>

--- a/artfynd/A 55743-2023 artfynd.xlsx
+++ b/artfynd/A 55743-2023 artfynd.xlsx
@@ -2554,7 +2554,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123336849</v>
+        <v>123334834</v>
       </c>
       <c r="B17" t="n">
         <v>98079</v>
@@ -2598,10 +2598,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>463066</v>
+        <v>463076</v>
       </c>
       <c r="R17" t="n">
-        <v>6295448</v>
+        <v>6295442</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2666,7 +2666,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123336769</v>
+        <v>123334183</v>
       </c>
       <c r="B18" t="n">
         <v>98079</v>
@@ -2710,13 +2710,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>463056</v>
+        <v>463078</v>
       </c>
       <c r="R18" t="n">
-        <v>6295451</v>
+        <v>6295459</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>75</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Dellokal</t>
+          <t>Riklig med bladrosetter påträffade på 4 olika dellokaler. Totalt 50 vinterståndare.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2778,7 +2778,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123334183</v>
+        <v>123336849</v>
       </c>
       <c r="B19" t="n">
         <v>98079</v>
@@ -2822,13 +2822,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>463078</v>
+        <v>463066</v>
       </c>
       <c r="R19" t="n">
-        <v>6295459</v>
+        <v>6295448</v>
       </c>
       <c r="S19" t="n">
-        <v>75</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2862,7 +2862,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Riklig med bladrosetter påträffade på 4 olika dellokaler. Totalt 50 vinterståndare.</t>
+          <t>Dellokal</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2890,7 +2890,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123334834</v>
+        <v>123334925</v>
       </c>
       <c r="B20" t="n">
         <v>98079</v>
@@ -2934,10 +2934,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>463076</v>
+        <v>463069</v>
       </c>
       <c r="R20" t="n">
-        <v>6295442</v>
+        <v>6295438</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -3002,7 +3002,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123334925</v>
+        <v>123336769</v>
       </c>
       <c r="B21" t="n">
         <v>98079</v>
@@ -3046,10 +3046,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>463069</v>
+        <v>463056</v>
       </c>
       <c r="R21" t="n">
-        <v>6295438</v>
+        <v>6295451</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
